--- a/output/crm_cleaned.xlsx
+++ b/output/crm_cleaned.xlsx
@@ -11,10 +11,12 @@
     <sheet name="Disqualified Leads" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Cleaning Log" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Channel &amp; CRM Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="City Prioritisation" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Cleaned Dataset'!$A$2:$AL$166</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Disqualified Leads'!$A$1:$AL$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'City Prioritisation'!$A$2:$L$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -34376,4 +34378,564 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="15" customWidth="1" min="11" max="11"/>
+    <col width="40" customWidth="1" min="12" max="12"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Ranked by priority_score (density 25% + spend potential 35% + pipeline warmth 25% + win rate 15%, each normalised 0-1 across cities). priority_reasoning spells out the real numbers behind every score - never trust the score alone without reading it. Physical Store leads with a known city only; online resellers are reached by DM, not a city visit, and leads with no city can't inform this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>city</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>qualified_leads</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>total_monthly_spend_potential_gbp</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>avg_monthly_spend_gbp</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>warm_leads</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>warm_ratio</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>won_customers</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>lost_or_churned</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>win_rate</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>priority_score</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>priority_rank</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>priority_reasoning</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>London</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>52</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>157673</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>3032</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>19</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="H3" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.765</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>52 qualified physical-store leads (#1 of 11 by density); an estimated £157,673/month combined spend potential (#1 of 11); 37% of the pipeline already warm (Engaged/Opportunity) (#7 of 11); a 18% win rate (2 won vs 9 lost/churned).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Brighton</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>22078</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>2453</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
+        <is>
+          <t>9 qualified physical-store leads (#2 of 11 by density); an estimated £22,078/month combined spend potential (#3 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Amsterdam</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>11752</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>3917</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>3 qualified physical-store leads (#10 of 11 by density); an estimated £11,752/month combined spend potential (#7 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>30547</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>4364</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="K6" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>7 qualified physical-store leads (#3 of 11 by density); an estimated £30,547/month combined spend potential (#2 of 11); 43% of the pipeline already warm (Engaged/Opportunity) (#6 of 11); a 50% win rate (1 won vs 1 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Leeds</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>3778</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1259</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="K7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>3 qualified physical-store leads (#10 of 11 by density); an estimated £3,778/month combined spend potential (#11 of 11); 67% of the pipeline already warm (Engaged/Opportunity) (#1 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Los Angeles</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>20889</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>5222</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £20,889/month combined spend potential (#4 of 11); 50% of the pipeline already warm (Engaged/Opportunity) (#4 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Glasgow</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>9395</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>2349</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.261</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £9,395/month combined spend potential (#10 of 11); 25% of the pipeline already warm (Engaged/Opportunity) (#9 of 11); a 100% win rate (1 won vs 0 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>Berlin</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>4</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>9874</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>2468</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>8</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>4 qualified physical-store leads (#7 of 11 by density); an estimated £9,874/month combined spend potential (#9 of 11); 50% of the pipeline already warm (Engaged/Opportunity) (#4 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Bristol</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>6</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>13369</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>2228</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>6 qualified physical-store leads (#4 of 11 by density); an estimated £13,369/month combined spend potential (#6 of 11); 33% of the pipeline already warm (Engaged/Opportunity) (#8 of 11); a 0% win rate (0 won vs 1 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>New York</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>13421</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>2684</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.107</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>10</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>5 qualified physical-store leads (#5 of 11 by density); an estimated £13,421/month combined spend potential (#5 of 11); 20% of the pipeline already warm (Engaged/Opportunity) (#10 of 11); a 0% win rate (0 won vs 2 lost/churned) - small sample, treat as directional only.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Manchester</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>11027</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2205</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.077</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>11</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>5 qualified physical-store leads (#5 of 11 by density); an estimated £11,027/month combined spend potential (#8 of 11); 0% of the pipeline already warm (Engaged/Opportunity) (#11 of 11); no won/lost history yet to judge receptiveness.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:L13"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>